--- a/01_TechHash_Internship_Tests/Vercel_Students_Assessment_Results.xlsx
+++ b/01_TechHash_Internship_Tests/Vercel_Students_Assessment_Results.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidate_Scores" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question_Breakdown" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Submissions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Question_Breakdown" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,17 +505,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Live Vercel Verification Test</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>VERCEL_TEST_999</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -523,25 +524,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -553,14 +554,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-17T07:29:18.149028+00:00</t>
+          <t>2026-10-01T09:22:12.743124+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +610,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-17T07:29:14.301357+00:00</t>
+          <t>2026-09-17T07:29:18.149028+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -665,14 +666,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-17T06:49:37.882273+00:00</t>
+          <t>2026-09-17T07:29:14.301357+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -721,14 +722,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-17T06:49:30.282813+00:00</t>
+          <t>2026-09-17T06:49:37.882273+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -747,22 +748,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>19</v>
@@ -777,14 +778,14 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-10T06:15:11.394857+00:00</t>
+          <t>2026-09-17T06:49:30.282813+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -803,13 +804,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -833,24 +834,24 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-10T06:15:07.611978+00:00</t>
+          <t>2026-09-10T06:15:11.394857+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ananya Reddy</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22341A05BULK1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -859,25 +860,25 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -889,24 +890,24 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-07T18:16:45.491072+00:00</t>
+          <t>2026-09-10T06:15:07.611978+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>22341A05BULK1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,13 +916,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="H9" t="n">
         <v>5</v>
@@ -945,19 +946,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-07T18:04:49.649062+00:00</t>
+          <t>2026-09-07T18:16:45.491072+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05TIER1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -971,19 +972,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" t="n">
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1001,7 +1002,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-07T17:48:49.362266+00:00</t>
+          <t>2026-09-07T18:04:49.649062+00:00</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1057,62 @@
         </is>
       </c>
       <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-07T17:48:49.362266+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G12" t="n">
+        <v>95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2026-09-07T17:46:40.648634+00:00</t>
         </is>
@@ -1072,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K138"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,98 +1150,194 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Question ID</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Scenario Question</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Topic</t>
+          <t>Student Written Solution</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Word Count</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Student Answer</t>
+          <t>Marks Awarded</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Correct Option</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Is Correct</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Marks Awarded</t>
+          <t>Submitted At</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Live Vercel Verification Test</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>VERCEL_TEST_999</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>Live Audio &amp; Speech-to-Text Pipeline</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Complete live architecture test via Vercel endpoint.</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:22:12.743124+00:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Roll Number</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Question ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Student Answer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Correct Option</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Is Correct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Marks Awarded</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Live Vercel Verification Test</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>VERCEL_TEST_999</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ai_scenario_01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Real-World Scenarios</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
-        </is>
-      </c>
+          <t>Live Audio &amp; Speech-to-Text Pipeline</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>Complete live architecture test via Vercel endpoint.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Evaluated by Engineering Rubrics</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1205,7 +1358,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1215,22 +1368,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1260,7 +1413,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1270,22 +1423,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1315,7 +1468,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1325,12 +1478,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1340,7 +1493,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1370,7 +1523,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1380,12 +1533,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1425,7 +1578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1435,12 +1588,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1480,7 +1633,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1490,12 +1643,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1505,7 +1658,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1535,7 +1688,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1545,12 +1698,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1560,7 +1713,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1590,7 +1743,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1600,12 +1753,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1645,7 +1798,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1655,12 +1808,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1670,7 +1823,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1700,7 +1853,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1710,12 +1863,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1725,7 +1878,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1755,7 +1908,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1765,12 +1918,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1810,7 +1963,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1820,12 +1973,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1865,7 +2018,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1875,12 +2028,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1890,7 +2043,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1920,7 +2073,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1930,12 +2083,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1975,7 +2128,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1985,12 +2138,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2000,7 +2153,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2030,7 +2183,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2040,12 +2193,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2055,7 +2208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2085,7 +2238,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2095,12 +2248,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2110,7 +2263,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2140,7 +2293,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2150,12 +2303,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2165,7 +2318,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2195,7 +2348,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2205,12 +2358,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2235,7 +2388,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2250,7 +2403,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2260,22 +2413,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2305,7 +2458,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2315,17 +2468,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2360,7 +2513,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2370,12 +2523,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2385,7 +2538,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2415,7 +2568,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2425,12 +2578,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2440,7 +2593,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2470,7 +2623,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2480,12 +2633,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2495,7 +2648,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2525,7 +2678,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2535,12 +2688,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2580,7 +2733,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2590,12 +2743,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2605,7 +2758,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2635,7 +2788,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2645,12 +2798,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2660,7 +2813,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2690,7 +2843,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2700,12 +2853,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2745,7 +2898,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2755,12 +2908,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2770,7 +2923,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2800,7 +2953,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2810,12 +2963,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2825,7 +2978,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2855,7 +3008,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2865,12 +3018,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2880,7 +3033,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2910,7 +3063,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2920,12 +3073,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2935,7 +3088,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2965,7 +3118,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2975,12 +3128,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2990,7 +3143,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3020,7 +3173,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3030,12 +3183,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3045,7 +3198,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3075,7 +3228,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3085,12 +3238,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3100,7 +3253,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3130,7 +3283,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3140,12 +3293,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3155,7 +3308,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3185,7 +3338,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3195,12 +3348,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3210,7 +3363,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3240,7 +3393,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3250,12 +3403,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3265,7 +3418,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3295,7 +3448,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3305,12 +3458,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3320,7 +3473,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3335,7 +3488,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3350,7 +3503,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3360,12 +3513,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3405,7 +3558,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3415,22 +3568,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3460,7 +3613,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3470,22 +3623,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3515,7 +3668,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3525,12 +3678,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3540,7 +3693,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3570,7 +3723,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3580,12 +3733,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3625,7 +3778,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3635,12 +3788,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3680,7 +3833,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3690,12 +3843,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3705,7 +3858,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3735,7 +3888,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3745,12 +3898,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3760,7 +3913,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3790,7 +3943,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3800,12 +3953,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3845,7 +3998,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3855,12 +4008,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3870,7 +4023,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3900,7 +4053,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3910,12 +4063,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3925,7 +4078,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3955,7 +4108,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3965,12 +4118,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4010,7 +4163,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4020,12 +4173,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4065,7 +4218,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4075,12 +4228,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4090,7 +4243,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4120,7 +4273,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4130,12 +4283,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4175,7 +4328,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4185,12 +4338,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4200,7 +4353,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4230,7 +4383,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4240,12 +4393,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4255,7 +4408,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4285,7 +4438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4295,12 +4448,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4310,7 +4463,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4340,7 +4493,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4350,12 +4503,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4365,7 +4518,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4395,7 +4548,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4405,12 +4558,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4435,7 +4588,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4450,7 +4603,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4460,12 +4613,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4475,7 +4628,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4505,7 +4658,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4515,22 +4668,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>A</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4560,7 +4713,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4570,22 +4723,22 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4615,7 +4768,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4625,12 +4778,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4640,7 +4793,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4670,7 +4823,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4680,12 +4833,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4695,7 +4848,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4725,7 +4878,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4735,12 +4888,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4750,7 +4903,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4780,7 +4933,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4790,12 +4943,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4805,7 +4958,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4835,7 +4988,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4845,12 +4998,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4860,7 +5013,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4890,7 +5043,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4900,12 +5053,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4915,7 +5068,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4945,7 +5098,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4955,12 +5108,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4970,7 +5123,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5000,7 +5153,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5010,12 +5163,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5025,7 +5178,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5055,7 +5208,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5065,12 +5218,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5110,7 +5263,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5120,12 +5273,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5165,7 +5318,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5175,12 +5328,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5220,7 +5373,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5230,12 +5383,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5245,7 +5398,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5275,7 +5428,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5285,12 +5438,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5330,7 +5483,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5340,12 +5493,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5385,7 +5538,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5395,12 +5548,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5410,7 +5563,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5440,7 +5593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5450,12 +5603,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5495,7 +5648,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5505,12 +5658,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5520,7 +5673,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5535,7 +5688,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5550,7 +5703,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5560,12 +5713,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5575,7 +5728,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5605,7 +5758,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5615,12 +5768,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5630,7 +5783,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5660,7 +5813,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5670,12 +5823,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5685,7 +5838,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5715,7 +5868,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5725,12 +5878,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5740,7 +5893,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5770,7 +5923,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5780,12 +5933,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5825,7 +5978,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5835,12 +5988,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5880,7 +6033,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5890,31 +6043,31 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5935,7 +6088,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5945,31 +6098,31 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -5990,7 +6143,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6000,12 +6153,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6045,7 +6198,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6055,12 +6208,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6070,7 +6223,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6100,7 +6253,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6110,12 +6263,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6125,7 +6278,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6155,7 +6308,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6165,12 +6318,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6210,7 +6363,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6220,12 +6373,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6265,7 +6418,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6275,12 +6428,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6290,7 +6443,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6320,7 +6473,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6330,12 +6483,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6375,7 +6528,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6385,12 +6538,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6553,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6430,7 +6583,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6440,12 +6593,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6455,7 +6608,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6485,7 +6638,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6495,12 +6648,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6510,7 +6663,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6540,7 +6693,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6550,12 +6703,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6565,7 +6718,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6595,7 +6748,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6605,12 +6758,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6635,7 +6788,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6650,7 +6803,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6660,31 +6813,31 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -6705,7 +6858,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6715,31 +6868,31 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6760,7 +6913,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6770,12 +6923,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6815,7 +6968,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6825,12 +6978,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6840,7 +6993,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6870,7 +7023,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6880,12 +7033,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6895,7 +7048,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6925,7 +7078,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6935,12 +7088,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6950,7 +7103,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6980,7 +7133,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6990,12 +7143,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7035,7 +7188,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7045,12 +7198,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7060,7 +7213,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7090,7 +7243,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7100,12 +7253,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7115,7 +7268,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7145,7 +7298,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7155,12 +7308,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7170,7 +7323,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7200,7 +7353,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7210,12 +7363,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7255,7 +7408,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7265,12 +7418,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7280,7 +7433,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7310,7 +7463,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7320,12 +7473,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7335,7 +7488,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7365,7 +7518,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7375,12 +7528,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7420,7 +7573,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7430,12 +7583,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7445,7 +7598,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7475,7 +7628,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7485,12 +7638,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7500,7 +7653,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7530,7 +7683,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7540,12 +7693,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7555,7 +7708,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7585,7 +7738,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7595,12 +7748,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7640,7 +7793,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7650,12 +7803,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7665,7 +7818,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7695,7 +7848,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7705,12 +7858,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7735,40 +7888,56 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ananya Reddy</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22341A05BULK1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>rn_002</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+          <t>Security and Architecture</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7790,12 +7959,12 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Aptitude</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Probability</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -7807,58 +7976,46 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>22341A05BULK1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>q1</t>
-        </is>
-      </c>
+          <t>Full Stack Developer Intern</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Time and Work</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125">
@@ -7879,7 +8036,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>q1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7895,12 +8052,12 @@
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7930,28 +8087,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>q2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
+          <t>Aptitude</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Docker &amp; Containers</t>
+          <t>Time and Work</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7981,37 +8138,37 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>q4</t>
+          <t>q3</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Computer_Fundamentals</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
+          <t>Docker &amp; Containers</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -8032,48 +8189,48 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>q5</t>
+          <t>q4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Binary Search</t>
+          <t>Sentence Correction</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>def search(): return 0</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Valid Code</t>
+          <t>Option D</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K128" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05TIER1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8081,23 +8238,39 @@
           <t>Cloud / DevOps Engineer Intern</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>q5</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>def search(): return 0</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Valid Code</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130">
@@ -8154,7 +8327,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Aptitude</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -8189,7 +8362,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -8224,7 +8397,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Computer_Fundamentals</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
@@ -8237,7 +8410,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -8259,7 +8432,7 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
@@ -8272,7 +8445,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135">
@@ -8329,7 +8502,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Aptitude</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
@@ -8364,7 +8537,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
+          <t>Verbal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -8399,7 +8572,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Computer_Fundamentals</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -8412,6 +8585,41 @@
         </is>
       </c>
       <c r="K138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
         <v>10</v>
       </c>
     </row>

--- a/01_TechHash_Internship_Tests/Vercel_Students_Assessment_Results.xlsx
+++ b/01_TechHash_Internship_Tests/Vercel_Students_Assessment_Results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,17 +505,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Live Vercel Verification Test</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VERCEL_TEST_999</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>71.43000000000001</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-01T09:22:12.743124+00:00</t>
+          <t>2026-10-01T09:39:43.428430+00:00</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,22 +583,22 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -610,24 +610,24 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-17T07:29:18.149028+00:00</t>
+          <t>2026-10-01T09:39:43.165295+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Live Vercel Verification Test</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>VERCEL_TEST_999</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -666,7 +666,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-17T07:29:14.301357+00:00</t>
+          <t>2026-10-01T09:22:12.743124+00:00</t>
         </is>
       </c>
     </row>
@@ -722,14 +722,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-17T06:49:37.882273+00:00</t>
+          <t>2026-09-17T07:29:18.149028+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-17T06:49:30.282813+00:00</t>
+          <t>2026-09-17T07:29:14.301357+00:00</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>19</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-10T06:15:11.394857+00:00</t>
+          <t>2026-09-17T06:49:37.882273+00:00</t>
         </is>
       </c>
     </row>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>19</v>
@@ -890,24 +890,24 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-10T06:15:07.611978+00:00</t>
+          <t>2026-09-17T06:49:30.282813+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ananya Reddy</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22341A05BULK1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -916,25 +916,25 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17.5</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>87.5</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -946,24 +946,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-07T18:16:45.491072+00:00</t>
+          <t>2026-09-10T06:15:11.394857+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-07T18:04:49.649062+00:00</t>
+          <t>2026-09-10T06:15:07.611978+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05BULK1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>95</v>
+        <v>87.5</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1058,19 +1058,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-07T17:48:49.362266+00:00</t>
+          <t>2026-09-07T18:16:45.491072+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05TIER1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1084,19 +1084,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1113,6 +1113,118 @@
         </is>
       </c>
       <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:49.649062+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" t="n">
+        <v>95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-07T17:48:49.362266+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" t="n">
+        <v>95</v>
+      </c>
+      <c r="H14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2026-09-07T17:46:40.648634+00:00</t>
         </is>
@@ -1129,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1182,37 +1294,137 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Mylavarapu Sruthi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24E51A05G8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Backend &amp; Full Stack Intern</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Asynchronous Distributed Queues &amp; Rate Limiting</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Scenario 1: High-Volume AI Document Processing Pipeline  [25 Marks]
+TechHash is building an enterprise document processing service. Users upload batches of invoices and reports (up to 5,000 files per batch). The backend runs OCR followed by structured LLM extraction. The OCR service is fast, but the LLM provider imposes a strict rate limit of 60 requests per minute. Each file takes 10–30 seconds. The client cannot hold an HTTP connection open and needs live, persistent progress tracking.
+Design the backend architecture step-by-step:
+1. Job creation, storage, and asynchronous queueing (batch vs individual task model, durable message queues).
+2. Worker concurrency control and strict rate-limiting (throttling outbound calls to 60 req/min).
+3. Fault tolerance, idempotency, exponential backoff retries, and dead-letter queues (DLQ).
+4. Frontend communication mechanism (SSE, WebSockets, or polling) and production observability metrics.
+(Write a structured engineering answer covering all 4 points. 150–400 words recommended.)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:39:43.428430+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mylavarapu Sruthi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24E51A05G8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Backend &amp; Full Stack Intern</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Database Performance &amp; Incident Diagnostics</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Scenario 2: Diagnosing a Post-Deployment Latency Regression  [25 Marks]
+Immediately following a backend deployment, API p99 latency escalates from 200 ms to 3.0 seconds. Server CPU and RAM usage remain normal, but database connection pool utilization approaches 100%. The regression is most severe on endpoints retrieving dashboard statistics and related entity collections. Incoming request volume has not noticeably changed.
+Describe your systematic, evidence-driven incident investigation:
+1. Observability data: APM traces, connection pool metrics, slow query logs, transaction durations.
+2. Database diagnosis: Root cause analysis focusing on query amplification (N+1 query regressions, missing indexes, unindexed joins, uncommitted locks).
+3. Immediate mitigation strategies to protect service availability (rollback, connection pool adjustments, circuit breakers, rate shaping).
+4. Permanent architectural remedies (eager loading, batching, caching, connection pooling policies, automated regression tests).
+(Write a structured engineering answer covering all 4 points. 150–400 words recommended.)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:39:43.428430+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Live Vercel Verification Test</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>VERCEL_TEST_999</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>AI Engineer Intern</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Live Audio &amp; Speech-to-Text Pipeline</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Complete live architecture test via Vercel endpoint.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G4" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H4" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>2026-10-01T09:22:12.743124+00:00</t>
         </is>
@@ -1229,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,43 +1504,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Live Vercel Verification Test</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VERCEL_TEST_999</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ai_scenario_01</t>
+          <t>bfs_06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real-World Scenarios</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Live Audio &amp; Speech-to-Text Pipeline</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Rate limiting  An API should allow short bursts of traffic while enforcing an average request rate over time. Which mechanism is designed for this behavior?</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Complete live architecture test via Vercel endpoint.</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Evaluated by Engineering Rubrics</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1337,43 +1553,43 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>bfs_08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Container Orchestration</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>Container orchestration  A Kubernetes service should only receive traffic after a newly started application instance has finished initializing and is ready to serve requests. Which feature is intended for this?</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1398,47 +1614,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>bfs_01</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>HTTP Semantics</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>HTTP semantics  A client sends an operation that replaces the complete resource at /api/users/42. The same request may be safely retried because sending it again should leave the resource in the same intended state. Which HTTP method best matches this behavior?</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1453,37 +1669,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>bfs_07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Caching / Cache-Aside</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>Caching  Your application uses the cache-aside pattern. A requested product is not present in the cache. What should normally happen next?</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1493,7 +1709,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1508,37 +1724,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>bfs_09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Authentication &amp; Security</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Authentication and security  A user password must be stored so that an attacker who obtains the database cannot directly recover the original password. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1548,7 +1764,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1563,37 +1779,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>bfs_03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Database Access Patterns</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>Database access patterns  An endpoint loads 80 orders and then executes one additional customer query for each order. The endpoint therefore performs 81 database queries for a single request. What backend problem is this?</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1618,37 +1834,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>bfs_02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Composite Index</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Composite indexes  A table has a composite index on (user_id, created_at). Which query is most likely to benefit directly from that index?</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1673,37 +1889,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>bfs_04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Transaction Isolation</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>Transaction isolation  Two concurrent transactions are reading and updating account balances. You need to prevent a transaction from reading data written by another transaction that has not committed yet. Which isolation level is the lowest standard level that prevents dirty reads?</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1713,7 +1929,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1728,37 +1944,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>bfs_10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Node.js Runtime Performance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>Node.js runtime  A Node.js API becomes very slow whenever a request triggers a large CPU-intensive image transformation. Database latency remains normal. What is the most likely explanation?</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1768,7 +1984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1783,37 +1999,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>bfs_05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Backend &amp; Full Stack</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Distributed Systems / CAP</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>Distributed systems  A service is replicated across multiple nodes and network communication between nodes can fail. According to the CAP theorem, during a network partition a distributed system must trade off which pair?</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1823,7 +2039,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1838,37 +2054,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>bfs_scenario_01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Real-World Scenarios</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Asynchronous Distributed Queues &amp; Rate Limiting</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>Scenario 1: High-Volume AI Document Processing Pipeline  [25 Marks]
+TechHash is building an enterprise document processing service. Users upload batches of invoices and reports (up to 5,000 files per batch). The backend runs OCR followed by structured LLM extraction. The OCR service is fast, but the LLM provider imposes a strict rate limit of 60 requests per minute. Each file takes 10–30 seconds. The client cannot hold an HTTP connection open and needs live, persistent progress tracking.
+Design the backend architecture step-by-step:
+1. Job creation, storage, and asynchronous queueing (batch vs individual task model, durable message queues).
+2. Worker concurrency control and strict rate-limiting (throttling outbound calls to 60 req/min).
+3. Fault tolerance, idempotency, exponential backoff retries, and dead-letter queues (DLQ).
+4. Frontend communication mechanism (SSE, WebSockets, or polling) and production observability metrics.
+(Write a structured engineering answer covering all 4 points. 150–400 words recommended.)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1878,7 +2101,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Evaluated by Engineering Rubrics</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1893,37 +2116,44 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Mylavarapu Sruthi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>24E51A05G8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>Backend &amp; Full Stack Intern</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>bfs_scenario_02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Real-World Scenarios</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Database Performance &amp; Incident Diagnostics</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Scenario 2: Diagnosing a Post-Deployment Latency Regression  [25 Marks]
+Immediately following a backend deployment, API p99 latency escalates from 200 ms to 3.0 seconds. Server CPU and RAM usage remain normal, but database connection pool utilization approaches 100%. The regression is most severe on endpoints retrieving dashboard statistics and related entity collections. Incoming request volume has not noticeably changed.
+Describe your systematic, evidence-driven incident investigation:
+1. Observability data: APM traces, connection pool metrics, slow query logs, transaction durations.
+2. Database diagnosis: Root cause analysis focusing on query amplification (N+1 query regressions, missing indexes, unindexed joins, uncommitted locks).
+3. Immediate mitigation strategies to protect service availability (rollback, connection pool adjustments, circuit breakers, rate shaping).
+4. Permanent architectural remedies (eager loading, batching, caching, connection pooling policies, automated regression tests).
+(Write a structured engineering answer covering all 4 points. 150–400 words recommended.)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,7 +2163,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Evaluated by Engineering Rubrics</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1948,56 +2178,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Live Vercel Verification Test</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23E51A0561</t>
+          <t>VERCEL_TEST_999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mobile App Developer Intern</t>
+          <t>AI Engineer Intern</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>ai_scenario_01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mobile App Development</t>
+          <t>Real-World Scenarios</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
-        </is>
-      </c>
+          <t>Live Audio &amp; Speech-to-Text Pipeline</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>Complete live architecture test via Vercel endpoint.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Evaluated by Engineering Rubrics</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -2018,7 +2244,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2028,12 +2254,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2073,7 +2299,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2083,17 +2309,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2128,7 +2354,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2138,12 +2364,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2153,7 +2379,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2183,7 +2409,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2193,12 +2419,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2208,7 +2434,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2238,7 +2464,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2248,12 +2474,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2293,7 +2519,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2303,12 +2529,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2318,7 +2544,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2348,7 +2574,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2358,12 +2584,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2373,7 +2599,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2403,7 +2629,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2413,12 +2639,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2428,7 +2654,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2443,7 +2669,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2458,7 +2684,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2468,17 +2694,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2498,7 +2724,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2513,7 +2739,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2523,12 +2749,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2538,7 +2764,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2553,7 +2779,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2608,7 +2834,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2623,7 +2849,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2633,12 +2859,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2648,7 +2874,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2663,7 +2889,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2718,7 +2944,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2733,7 +2959,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2743,12 +2969,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2758,7 +2984,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2773,7 +2999,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2788,7 +3014,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2798,12 +3024,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2828,7 +3054,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2843,7 +3069,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2853,12 +3079,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2883,7 +3109,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2898,7 +3124,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2908,12 +3134,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2923,7 +3149,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2938,7 +3164,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2953,7 +3179,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2963,12 +3189,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2978,7 +3204,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2993,7 +3219,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3008,7 +3234,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3018,12 +3244,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3033,7 +3259,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3048,7 +3274,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dhanush Gopavaram</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3063,7 +3289,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3073,12 +3299,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3088,7 +3314,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3118,7 +3344,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3128,22 +3354,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3173,7 +3399,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3183,12 +3409,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3198,7 +3424,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3228,7 +3454,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3238,12 +3464,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3283,7 +3509,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3293,12 +3519,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3338,7 +3564,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3348,12 +3574,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3393,7 +3619,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3403,12 +3629,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3418,7 +3644,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3448,7 +3674,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3458,12 +3684,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3503,7 +3729,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3513,12 +3739,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3528,7 +3754,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3543,7 +3769,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3558,7 +3784,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3568,12 +3794,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3583,7 +3809,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3598,7 +3824,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3613,7 +3839,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3623,22 +3849,22 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3653,7 +3879,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3668,7 +3894,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3678,12 +3904,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3693,7 +3919,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3708,7 +3934,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3723,7 +3949,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3733,12 +3959,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3748,7 +3974,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3763,7 +3989,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3778,7 +4004,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3788,12 +4014,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3818,7 +4044,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3833,7 +4059,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3843,12 +4069,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3858,7 +4084,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3873,7 +4099,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3888,7 +4114,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3898,12 +4124,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3913,7 +4139,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3928,7 +4154,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3943,7 +4169,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3953,12 +4179,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3983,7 +4209,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3998,7 +4224,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4008,12 +4234,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4023,7 +4249,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4038,7 +4264,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4053,7 +4279,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4063,12 +4289,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4078,7 +4304,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4093,7 +4319,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4108,7 +4334,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4118,12 +4344,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4133,7 +4359,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4148,7 +4374,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Dhanush Gopavaram</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4163,7 +4389,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4173,12 +4399,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4218,7 +4444,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4228,12 +4454,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4273,7 +4499,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4283,17 +4509,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4328,7 +4554,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4338,12 +4564,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4353,7 +4579,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4383,7 +4609,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4393,12 +4619,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4408,7 +4634,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4438,7 +4664,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4448,12 +4674,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4493,7 +4719,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4503,12 +4729,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4518,7 +4744,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4548,7 +4774,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4558,12 +4784,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4573,7 +4799,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4603,7 +4829,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4613,12 +4839,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4628,7 +4854,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4643,7 +4869,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4658,7 +4884,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4668,12 +4894,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4683,7 +4909,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4698,7 +4924,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4713,7 +4939,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4723,22 +4949,22 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>A</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4753,7 +4979,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4768,7 +4994,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4778,12 +5004,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4793,7 +5019,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4808,7 +5034,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4823,7 +5049,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4833,12 +5059,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4848,7 +5074,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4863,7 +5089,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4878,7 +5104,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4888,12 +5114,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4903,7 +5129,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4918,7 +5144,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4933,7 +5159,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4943,12 +5169,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4958,7 +5184,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4973,7 +5199,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4988,7 +5214,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4998,12 +5224,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5013,7 +5239,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5028,7 +5254,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5043,7 +5269,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5053,12 +5279,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5083,7 +5309,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5098,7 +5324,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5108,12 +5334,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5138,7 +5364,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5153,7 +5379,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5163,12 +5389,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5178,7 +5404,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5193,7 +5419,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5208,7 +5434,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5218,12 +5444,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5233,7 +5459,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5248,7 +5474,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5263,7 +5489,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5273,12 +5499,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5288,7 +5514,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5318,7 +5544,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5328,12 +5554,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5343,7 +5569,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5373,7 +5599,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5383,22 +5609,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5428,7 +5654,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5438,12 +5664,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5453,7 +5679,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5483,7 +5709,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5493,12 +5719,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5508,7 +5734,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5538,7 +5764,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5548,12 +5774,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5593,7 +5819,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5603,12 +5829,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5618,7 +5844,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5648,7 +5874,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5658,12 +5884,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5703,7 +5929,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5713,12 +5939,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5728,7 +5954,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5743,7 +5969,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5758,7 +5984,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5768,12 +5994,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5798,7 +6024,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5813,7 +6039,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5823,12 +6049,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5838,7 +6064,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5853,7 +6079,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5868,7 +6094,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5878,12 +6104,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5893,7 +6119,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5908,7 +6134,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5923,7 +6149,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5933,12 +6159,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5963,7 +6189,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5978,7 +6204,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5988,12 +6214,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6018,7 +6244,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6033,7 +6259,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6043,12 +6269,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6073,7 +6299,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6088,7 +6314,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6098,37 +6324,37 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6143,7 +6369,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6153,12 +6379,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6183,7 +6409,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6198,7 +6424,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6208,12 +6434,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6238,7 +6464,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6253,7 +6479,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6263,12 +6489,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6278,7 +6504,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6293,7 +6519,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6308,7 +6534,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6318,12 +6544,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6348,7 +6574,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6363,7 +6589,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6373,12 +6599,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6388,7 +6614,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6418,7 +6644,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_001</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6428,12 +6654,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Mobile App Architecture</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6473,7 +6699,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_002</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6483,12 +6709,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Security and Architecture</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6528,7 +6754,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6538,12 +6764,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Full-Stack Technologies</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6553,7 +6779,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6583,7 +6809,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_004</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6593,12 +6819,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>API Connectivity</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6608,7 +6834,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6638,7 +6864,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6648,12 +6874,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6693,7 +6919,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6703,12 +6929,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6718,7 +6944,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6748,7 +6974,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6758,31 +6984,31 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -6803,7 +7029,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6813,12 +7039,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6828,7 +7054,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6843,7 +7069,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6858,7 +7084,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>rn_007</t>
+          <t>rn_009</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6868,37 +7094,37 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real-Time Communication</t>
+          <t>Network Debugging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6913,7 +7139,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>rn_006</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6923,12 +7149,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Data Update Flow</t>
+          <t>Database Selection</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6938,7 +7164,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6953,7 +7179,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6968,7 +7194,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>rn_017</t>
+          <t>rn_011</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6978,12 +7204,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Logical Deduction</t>
+          <t>Offline Architecture</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7008,7 +7234,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7023,7 +7249,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>rn_014</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7033,12 +7259,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Performance Troubleshooting</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7048,7 +7274,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7063,7 +7289,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7078,7 +7304,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>rn_016</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7088,12 +7314,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Number Pattern</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7103,7 +7329,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7118,7 +7344,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7133,7 +7359,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>rn_005</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7143,12 +7369,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>System Components</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7158,7 +7384,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7173,7 +7399,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7188,7 +7414,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>rn_013</t>
+          <t>rn_015</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7198,12 +7424,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>System Scalability</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7213,7 +7439,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7228,7 +7454,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7243,7 +7469,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>rn_008</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7253,12 +7479,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>API Reliability</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7268,7 +7494,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7283,7 +7509,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7298,7 +7524,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>rn_001</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7308,12 +7534,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mobile App Architecture</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7338,7 +7564,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7353,7 +7579,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>rn_019</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7363,12 +7589,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Direction Sense</t>
+          <t>Arithmetic</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7378,7 +7604,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7393,7 +7619,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7408,7 +7634,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>rn_020</t>
+          <t>rn_019</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7418,12 +7644,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Direction Sense</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7448,7 +7674,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>dhanush</t>
+          <t>Candidate</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7463,7 +7689,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>rn_018</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7473,12 +7699,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arithmetic</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7488,7 +7714,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7518,7 +7744,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>rn_010</t>
+          <t>rn_007</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7528,17 +7754,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Database Selection</t>
+          <t>Real-Time Communication</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+          <t>A Fixly technician app needs near real-time job status updates. Which choice is generally most suitable when the server must actively push frequent updates to connected users?</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(unattempted)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7548,11 +7774,11 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -7573,7 +7799,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>rn_003</t>
+          <t>rn_006</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7583,12 +7809,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Full-Stack Technologies</t>
+          <t>Data Update Flow</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+          <t>A user updates their phone number in the mobile app. Which sequence is the most appropriate for a secure implementation?</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7598,7 +7824,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7628,7 +7854,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>rn_012</t>
+          <t>rn_017</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7638,12 +7864,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Performance Troubleshooting</t>
+          <t>Logical Deduction</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+          <t>All mobile applications are software. All software must be tested before release. Which conclusion follows?</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7683,7 +7909,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>rn_009</t>
+          <t>rn_014</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7693,12 +7919,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Network Debugging</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+          <t>A user completes a payment successfully, but the app loses internet connectivity before receiving the final response. The user retries. Which backend design best prevents charging or recording the same transaction twice?</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7738,7 +7964,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>rn_011</t>
+          <t>rn_016</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7748,12 +7974,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Offline Architecture</t>
+          <t>Number Pattern</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+          <t>What is the next number in the sequence: 3, 6, 12, 24, ___?</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7763,7 +7989,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7793,7 +8019,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>rn_004</t>
+          <t>rn_005</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7803,12 +8029,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>API Connectivity</t>
+          <t>System Components</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+          <t>Which statement best explains the difference between a frontend framework, a backend framework, and a database?</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7848,7 +8074,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>rn_015</t>
+          <t>rn_013</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7858,12 +8084,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>System Scalability</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+          <t>You are designing an authentication system for a mobile application. Which approach is the MOST secure and architecturally appropriate?</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7873,7 +8099,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7903,7 +8129,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>rn_002</t>
+          <t>rn_008</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7913,12 +8139,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Security and Architecture</t>
+          <t>API Reliability</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+          <t>A mobile app sends a POST request to create a service booking, but the user taps the button repeatedly because the network is slow. Which backend design best reduces the risk of duplicate bookings?</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7943,274 +8169,322 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ananya Reddy</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>22341A05BULK1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>rn_001</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+          <t>Mobile App Architecture</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>A mobile application allows a user to submit a service request. Which architecture correctly describes the usual data flow?</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ananya Reddy</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22341A05BULK1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>rn_019</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+          <t>Direction Sense</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Ravi is facing north. He turns right, then left, and then right again. Which direction is he facing?</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K124" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>q1</t>
+          <t>rn_020</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Time and Work</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
+          <t>Ordering</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Task P must be completed before Q, Q before R, and R before S. Which order satisfies all conditions?</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>q2</t>
+          <t>rn_018</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aptitude</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Time and Work</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
+          <t>Arithmetic</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>One test run takes 6 minutes. How long will 5 test runs take if they run one after another?</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>rn_010</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Docker &amp; Containers</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
+          <t>Database Selection</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Which database choice is generally more appropriate when an application requires strong relationships, transactions, and consistent records for entities such as users, bookings, payments, and invoices?</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>q4</t>
+          <t>rn_003</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sentence Correction</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
+          <t>Full-Stack Technologies</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Which combination represents a valid full-stack mobile application architecture?</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Option D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8225,243 +8499,347 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Praveen Kumar</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>22341A05TIER1</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Mobile App Developer Intern</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>q5</t>
+          <t>rn_012</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Mobile App Development</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Binary Search</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>Performance Troubleshooting</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>A backend API is becoming slow as the number of users grows. Which investigation order is the most technically sound?</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>def search(): return 0</t>
+          <t>(unattempted)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Valid Code</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K129" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>rn_009</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Network Debugging</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>An API endpoint works correctly in Postman but the mobile application cannot access it on a real device. Which is the BEST first technical conclusion?</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>rn_011</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Offline Architecture</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>A mobile application must support offline usage. A technician may create service notes without internet and synchronize them later. Which architecture is the strongest approach?</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>rn_004</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Verbal</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>API Connectivity</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>A React Native app needs to retrieve a technician's profile from the server. Which approach is most appropriate?</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>rn_015</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>System Scalability</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>A mobile app, backend, and database are hosted as separate layers. The company wants to scale the system for a large increase in users. Which architecture change is generally the MOST appropriate?</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>dhanush</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>23E51A0561</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Mobile App Developer Intern</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>rn_002</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Coding</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+          <t>Mobile App Development</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Security and Architecture</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Why should a production mobile application generally NOT connect directly to a database such as MySQL or PostgreSQL?</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(unattempted)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K134" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05BULK1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -8470,7 +8848,11 @@
           <t>Aptitude</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
@@ -8486,26 +8868,30 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05BULK1</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer Intern</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aptitude</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
@@ -8515,18 +8901,18 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05TIER1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8534,16 +8920,32 @@
           <t>Cloud / DevOps Engineer Intern</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>q1</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Verbal</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Time and Work</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>YES</t>
@@ -8556,12 +8958,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CDC Test Candidate</t>
+          <t>Praveen Kumar</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>22341A05TEST</t>
+          <t>22341A05TIER1</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8569,16 +8971,32 @@
           <t>Cloud / DevOps Engineer Intern</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>q2</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Computer_Fundamentals</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Time and Work</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>YES</t>
@@ -8591,35 +9009,503 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>Praveen Kumar</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>22341A05TIER1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>q3</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Computer_Fundamentals</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Docker &amp; Containers</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Praveen Kumar</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>22341A05TIER1</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>q4</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Verbal</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Sentence Correction</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Praveen Kumar</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>22341A05TIER1</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>q5</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>def search(): return 0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Valid Code</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
           <t>CDC Test Candidate</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>22341A05TEST</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Cloud / DevOps Engineer Intern</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Verbal</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Computer_Fundamentals</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
         <is>
           <t>Coding</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="K139" t="n">
+      <c r="K146" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aptitude</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Verbal</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Computer_Fundamentals</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CDC Test Candidate</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>22341A05TEST</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps Engineer Intern</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
         <v>10</v>
       </c>
     </row>
